--- a/Linux客户端全功能支持列表.xlsx
+++ b/Linux客户端全功能支持列表.xlsx
@@ -131,7 +131,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>test456789</t>
+    <t>test</t>
   </si>
   <si>
     <t>基本策略</t>

--- a/Linux客户端全功能支持列表.xlsx
+++ b/Linux客户端全功能支持列表.xlsx
@@ -131,7 +131,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>test</t>
+    <t>test88</t>
   </si>
   <si>
     <t>基本策略</t>

--- a/Linux客户端全功能支持列表.xlsx
+++ b/Linux客户端全功能支持列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="28800" windowHeight="11180"/>
   </bookViews>
   <sheets>
     <sheet name="模块划分ALL" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>test88</t>
+    <t>test8811</t>
   </si>
   <si>
     <t>基本策略</t>
@@ -4946,31 +4946,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V275"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="6.33333333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.6666666666667" style="16" customWidth="1"/>
-    <col min="3" max="3" width="18.6666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="34.1666666666667" style="2"/>
-    <col min="5" max="5" width="41.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="68.3333333333333" style="35" customWidth="1"/>
-    <col min="7" max="7" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="6.33035714285714" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.6696428571429" style="16" customWidth="1"/>
+    <col min="3" max="3" width="18.6696428571429" style="2" customWidth="1"/>
+    <col min="4" max="4" width="34.1696428571429" style="2"/>
+    <col min="5" max="5" width="41.6696428571429" style="2" customWidth="1"/>
+    <col min="6" max="6" width="68.3303571428571" style="35" customWidth="1"/>
+    <col min="7" max="7" width="20.6696428571429" style="2"/>
     <col min="8" max="8" width="19" style="4"/>
     <col min="9" max="10" width="17.5" style="4"/>
-    <col min="11" max="11" width="18.1666666666667" style="4"/>
+    <col min="11" max="11" width="18.1696428571429" style="4"/>
     <col min="12" max="13" width="13" style="4"/>
-    <col min="14" max="14" width="13.1666666666667" style="4"/>
+    <col min="14" max="14" width="13.1696428571429" style="4"/>
     <col min="15" max="15" width="5" style="4"/>
-    <col min="16" max="16" width="10.1666666666667" style="4"/>
-    <col min="17" max="17" width="3.66666666666667" style="4"/>
+    <col min="16" max="16" width="10.1696428571429" style="4"/>
+    <col min="17" max="17" width="3.66964285714286" style="4"/>
     <col min="18" max="18" width="5" style="4"/>
-    <col min="19" max="19" width="3.16666666666667" style="4"/>
+    <col min="19" max="19" width="3.16964285714286" style="4"/>
     <col min="20" max="21" width="9" style="4"/>
     <col min="22" max="22" width="13" style="4"/>
     <col min="23" max="27" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:22">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:22">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -5000,7 +5000,7 @@
       <c r="U1" s="32"/>
       <c r="V1" s="32"/>
     </row>
-    <row r="2" s="1" customFormat="1" ht="12" spans="1:22">
+    <row r="2" s="1" customFormat="1" ht="16" spans="1:22">
       <c r="A2" s="59" t="s">
         <v>3</v>
       </c>
@@ -5100,7 +5100,7 @@
       <c r="U4" s="11"/>
       <c r="V4" s="12"/>
     </row>
-    <row r="5" ht="36" spans="1:22">
+    <row r="5" ht="46" spans="1:22">
       <c r="A5" s="63"/>
       <c r="B5" s="65"/>
       <c r="C5" s="65" t="s">
@@ -5132,7 +5132,7 @@
       <c r="U5" s="11"/>
       <c r="V5" s="12"/>
     </row>
-    <row r="6" ht="48" spans="1:22">
+    <row r="6" ht="61" spans="1:22">
       <c r="A6" s="63"/>
       <c r="B6" s="65"/>
       <c r="C6" s="65" t="s">
@@ -5472,7 +5472,7 @@
       <c r="U16" s="11"/>
       <c r="V16" s="12"/>
     </row>
-    <row r="17" ht="24" spans="1:22">
+    <row r="17" ht="31" spans="1:22">
       <c r="A17" s="63">
         <v>2</v>
       </c>
@@ -5599,7 +5599,7 @@
       <c r="U20" s="11"/>
       <c r="V20" s="12"/>
     </row>
-    <row r="21" ht="24" spans="1:22">
+    <row r="21" ht="31" spans="1:22">
       <c r="A21" s="63">
         <v>3</v>
       </c>
@@ -5725,7 +5725,7 @@
       <c r="U24" s="11"/>
       <c r="V24" s="12"/>
     </row>
-    <row r="25" s="45" customFormat="1" ht="12" spans="1:22">
+    <row r="25" s="45" customFormat="1" ht="16" spans="1:22">
       <c r="A25" s="63">
         <v>4</v>
       </c>
@@ -5759,7 +5759,7 @@
       <c r="U25" s="9"/>
       <c r="V25" s="19"/>
     </row>
-    <row r="26" s="45" customFormat="1" ht="12" spans="1:22">
+    <row r="26" s="45" customFormat="1" ht="16" spans="1:22">
       <c r="A26" s="63"/>
       <c r="B26" s="69"/>
       <c r="C26" s="70" t="s">
@@ -5855,7 +5855,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="12"/>
     </row>
-    <row r="29" ht="36" spans="1:22">
+    <row r="29" ht="46" spans="1:22">
       <c r="A29" s="63"/>
       <c r="B29" s="64"/>
       <c r="C29" s="65" t="s">
@@ -6051,7 +6051,7 @@
       <c r="U34" s="11"/>
       <c r="V34" s="12"/>
     </row>
-    <row r="35" ht="48" spans="1:22">
+    <row r="35" ht="61" spans="1:22">
       <c r="A35" s="63"/>
       <c r="B35" s="69"/>
       <c r="C35" s="70" t="s">
@@ -6181,7 +6181,7 @@
       <c r="U38" s="9"/>
       <c r="V38" s="19"/>
     </row>
-    <row r="39" s="46" customFormat="1" ht="12" spans="1:22">
+    <row r="39" s="46" customFormat="1" ht="16" spans="1:22">
       <c r="A39" s="63"/>
       <c r="B39" s="64"/>
       <c r="C39" s="65" t="s">
@@ -6211,7 +6211,7 @@
       <c r="U39" s="9"/>
       <c r="V39" s="19"/>
     </row>
-    <row r="40" s="46" customFormat="1" ht="24" spans="1:22">
+    <row r="40" s="46" customFormat="1" ht="31" spans="1:22">
       <c r="A40" s="63"/>
       <c r="B40" s="64"/>
       <c r="C40" s="65" t="s">
@@ -6275,7 +6275,7 @@
       <c r="U41" s="9"/>
       <c r="V41" s="19"/>
     </row>
-    <row r="42" ht="24" spans="1:22">
+    <row r="42" ht="31" spans="1:22">
       <c r="A42" s="63"/>
       <c r="B42" s="69"/>
       <c r="C42" s="70" t="s">
@@ -6907,7 +6907,7 @@
       <c r="U61" s="9"/>
       <c r="V61" s="9"/>
     </row>
-    <row r="62" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="62" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A62" s="63"/>
       <c r="B62" s="74"/>
       <c r="C62" s="65" t="s">
@@ -6967,7 +6967,7 @@
       <c r="U63" s="9"/>
       <c r="V63" s="9"/>
     </row>
-    <row r="64" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="64" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A64" s="63"/>
       <c r="B64" s="74"/>
       <c r="C64" s="65" t="s">
@@ -6997,7 +6997,7 @@
       <c r="U64" s="9"/>
       <c r="V64" s="9"/>
     </row>
-    <row r="65" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="65" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A65" s="63"/>
       <c r="B65" s="74"/>
       <c r="C65" s="65" t="s">
@@ -7027,7 +7027,7 @@
       <c r="U65" s="9"/>
       <c r="V65" s="9"/>
     </row>
-    <row r="66" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="66" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A66" s="63"/>
       <c r="B66" s="74"/>
       <c r="C66" s="65" t="s">
@@ -7087,7 +7087,7 @@
       <c r="U67" s="9"/>
       <c r="V67" s="9"/>
     </row>
-    <row r="68" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="68" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A68" s="63"/>
       <c r="B68" s="74"/>
       <c r="C68" s="65" t="s">
@@ -7149,7 +7149,7 @@
       <c r="U69" s="9"/>
       <c r="V69" s="9"/>
     </row>
-    <row r="70" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="70" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A70" s="63"/>
       <c r="B70" s="76" t="s">
         <v>113</v>
@@ -7183,7 +7183,7 @@
       <c r="U70" s="9"/>
       <c r="V70" s="9"/>
     </row>
-    <row r="71" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="71" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A71" s="63"/>
       <c r="B71" s="72"/>
       <c r="C71" s="73" t="s">
@@ -7213,7 +7213,7 @@
       <c r="U71" s="9"/>
       <c r="V71" s="9"/>
     </row>
-    <row r="72" s="47" customFormat="1" ht="24" spans="1:22">
+    <row r="72" s="47" customFormat="1" ht="31" spans="1:22">
       <c r="A72" s="63"/>
       <c r="B72" s="76" t="s">
         <v>117</v>
@@ -7277,7 +7277,7 @@
       <c r="U73" s="9"/>
       <c r="V73" s="9"/>
     </row>
-    <row r="74" s="47" customFormat="1" ht="24" spans="1:22">
+    <row r="74" s="47" customFormat="1" ht="31" spans="1:22">
       <c r="A74" s="63"/>
       <c r="B74" s="76" t="s">
         <v>121</v>
@@ -7311,7 +7311,7 @@
       <c r="U74" s="9"/>
       <c r="V74" s="9"/>
     </row>
-    <row r="75" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="75" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A75" s="63"/>
       <c r="B75" s="72"/>
       <c r="C75" s="73" t="s">
@@ -7341,7 +7341,7 @@
       <c r="U75" s="9"/>
       <c r="V75" s="9"/>
     </row>
-    <row r="76" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="76" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A76" s="63"/>
       <c r="B76" s="72"/>
       <c r="C76" s="73" t="s">
@@ -7435,7 +7435,7 @@
       <c r="U78" s="9"/>
       <c r="V78" s="9"/>
     </row>
-    <row r="79" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="79" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A79" s="63"/>
       <c r="B79" s="74"/>
       <c r="C79" s="65" t="s">
@@ -7465,7 +7465,7 @@
       <c r="U79" s="9"/>
       <c r="V79" s="9"/>
     </row>
-    <row r="80" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="80" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A80" s="63"/>
       <c r="B80" s="74"/>
       <c r="C80" s="65" t="s">
@@ -7521,7 +7521,7 @@
       <c r="U81" s="79"/>
       <c r="V81" s="79"/>
     </row>
-    <row r="82" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="82" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="B82" s="72" t="s">
         <v>131</v>
       </c>
@@ -7552,7 +7552,7 @@
       <c r="U82" s="81"/>
       <c r="V82" s="81"/>
     </row>
-    <row r="83" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="83" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A83" s="63"/>
       <c r="B83" s="70"/>
       <c r="C83" s="73" t="s">
@@ -7582,7 +7582,7 @@
       <c r="U83" s="81"/>
       <c r="V83" s="81"/>
     </row>
-    <row r="84" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="84" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A84" s="63"/>
       <c r="B84" s="70"/>
       <c r="C84" s="73" t="s">
@@ -7612,7 +7612,7 @@
       <c r="U84" s="81"/>
       <c r="V84" s="81"/>
     </row>
-    <row r="85" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="85" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A85" s="63"/>
       <c r="B85" s="70"/>
       <c r="C85" s="73" t="s">
@@ -7642,7 +7642,7 @@
       <c r="U85" s="81"/>
       <c r="V85" s="81"/>
     </row>
-    <row r="86" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="86" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A86" s="63"/>
       <c r="B86" s="70"/>
       <c r="C86" s="73" t="s">
@@ -7672,7 +7672,7 @@
       <c r="U86" s="81"/>
       <c r="V86" s="81"/>
     </row>
-    <row r="87" s="47" customFormat="1" ht="14.4" spans="1:22">
+    <row r="87" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A87" s="63"/>
       <c r="B87" s="70"/>
       <c r="C87" s="73" t="s">
@@ -7702,7 +7702,7 @@
       <c r="U87" s="81"/>
       <c r="V87" s="81"/>
     </row>
-    <row r="88" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="88" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A88" s="63"/>
       <c r="B88" s="74" t="s">
         <v>138</v>
@@ -7734,7 +7734,7 @@
       <c r="U88" s="81"/>
       <c r="V88" s="81"/>
     </row>
-    <row r="89" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="89" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A89" s="63"/>
       <c r="B89" s="74"/>
       <c r="C89" s="82" t="s">
@@ -7764,7 +7764,7 @@
       <c r="U89" s="81"/>
       <c r="V89" s="81"/>
     </row>
-    <row r="90" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="90" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A90" s="63"/>
       <c r="B90" s="74"/>
       <c r="C90" s="82" t="s">
@@ -7794,7 +7794,7 @@
       <c r="U90" s="81"/>
       <c r="V90" s="81"/>
     </row>
-    <row r="91" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="91" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A91" s="63"/>
       <c r="B91" s="74"/>
       <c r="C91" s="82" t="s">
@@ -7824,7 +7824,7 @@
       <c r="U91" s="81"/>
       <c r="V91" s="81"/>
     </row>
-    <row r="92" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="92" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A92" s="63"/>
       <c r="B92" s="74"/>
       <c r="C92" s="82" t="s">
@@ -7854,7 +7854,7 @@
       <c r="U92" s="9"/>
       <c r="V92" s="9"/>
     </row>
-    <row r="93" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="93" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A93" s="63"/>
       <c r="B93" s="74"/>
       <c r="C93" s="82" t="s">
@@ -7884,7 +7884,7 @@
       <c r="U93" s="9"/>
       <c r="V93" s="83"/>
     </row>
-    <row r="94" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="94" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A94" s="63"/>
       <c r="B94" s="74"/>
       <c r="C94" s="82" t="s">
@@ -7914,7 +7914,7 @@
       <c r="U94" s="9"/>
       <c r="V94" s="83"/>
     </row>
-    <row r="95" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="95" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A95" s="63"/>
       <c r="B95" s="74"/>
       <c r="C95" s="82" t="s">
@@ -7944,7 +7944,7 @@
       <c r="U95" s="9"/>
       <c r="V95" s="83"/>
     </row>
-    <row r="96" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="96" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A96" s="63"/>
       <c r="B96" s="74"/>
       <c r="C96" s="82" t="s">
@@ -7974,7 +7974,7 @@
       <c r="U96" s="9"/>
       <c r="V96" s="83"/>
     </row>
-    <row r="97" s="47" customFormat="1" ht="15" spans="1:22">
+    <row r="97" s="47" customFormat="1" ht="16.8" spans="1:22">
       <c r="A97" s="63"/>
       <c r="B97" s="74"/>
       <c r="C97" s="82" t="s">
@@ -10258,7 +10258,7 @@
       <c r="U172" s="87"/>
       <c r="V172" s="87"/>
     </row>
-    <row r="173" s="47" customFormat="1" ht="36" spans="1:22">
+    <row r="173" s="47" customFormat="1" ht="46" spans="1:22">
       <c r="A173" s="88" t="s">
         <v>226</v>
       </c>
@@ -13364,28 +13364,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="基本策略"/>
   <dimension ref="A1:S55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="25.6666666666667" style="2"/>
-    <col min="3" max="3" width="61.8333333333333" style="35"/>
-    <col min="4" max="4" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="25.6696428571429" style="2"/>
+    <col min="3" max="3" width="61.8303571428571" style="35"/>
+    <col min="4" max="4" width="20.6696428571429" style="2"/>
     <col min="5" max="5" width="19" style="4"/>
     <col min="6" max="7" width="17.5" style="4"/>
-    <col min="8" max="8" width="18.1666666666667" style="4"/>
+    <col min="8" max="8" width="18.1696428571429" style="4"/>
     <col min="9" max="10" width="13" style="4"/>
-    <col min="11" max="11" width="13.1666666666667" style="4"/>
+    <col min="11" max="11" width="13.1696428571429" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="10.1666666666667" style="4"/>
-    <col min="14" max="14" width="3.66666666666667" style="4"/>
+    <col min="13" max="13" width="10.1696428571429" style="4"/>
+    <col min="14" max="14" width="3.66964285714286" style="4"/>
     <col min="15" max="15" width="5" style="4"/>
-    <col min="16" max="16" width="3.16666666666667" style="4"/>
+    <col min="16" max="16" width="3.16964285714286" style="4"/>
     <col min="17" max="18" width="9" style="4"/>
     <col min="19" max="19" width="13" style="4"/>
     <col min="20" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -14035,7 +14035,7 @@
       <c r="R26" s="11"/>
       <c r="S26" s="12"/>
     </row>
-    <row r="27" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="27" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A27" s="13" t="s">
         <v>570</v>
       </c>
@@ -14060,7 +14060,7 @@
       <c r="R27" s="9"/>
       <c r="S27" s="19"/>
     </row>
-    <row r="28" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="28" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A28" s="13" t="s">
         <v>571</v>
       </c>
@@ -14185,7 +14185,7 @@
       <c r="R32" s="11"/>
       <c r="S32" s="12"/>
     </row>
-    <row r="33" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="33" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A33" s="13" t="s">
         <v>575</v>
       </c>
@@ -14210,7 +14210,7 @@
       <c r="R33" s="9"/>
       <c r="S33" s="19"/>
     </row>
-    <row r="34" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="34" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A34" s="13" t="s">
         <v>576</v>
       </c>
@@ -14560,7 +14560,7 @@
       <c r="R47" s="9"/>
       <c r="S47" s="19"/>
     </row>
-    <row r="48" s="46" customFormat="1" ht="12" spans="1:19">
+    <row r="48" s="46" customFormat="1" ht="15.2" spans="1:19">
       <c r="A48" s="13" t="s">
         <v>590</v>
       </c>
@@ -14660,7 +14660,7 @@
       <c r="R51" s="11"/>
       <c r="S51" s="12"/>
     </row>
-    <row r="52" s="46" customFormat="1" ht="12" spans="1:19">
+    <row r="52" s="46" customFormat="1" ht="15.2" spans="1:19">
       <c r="A52" s="22" t="s">
         <v>594</v>
       </c>
@@ -14773,28 +14773,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="25.6666666666667" style="2"/>
-    <col min="3" max="3" width="61.8333333333333" style="35"/>
-    <col min="4" max="4" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="25.6696428571429" style="2"/>
+    <col min="3" max="3" width="61.8303571428571" style="35"/>
+    <col min="4" max="4" width="20.6696428571429" style="2"/>
     <col min="5" max="5" width="19" style="4"/>
     <col min="6" max="7" width="17.5" style="4"/>
-    <col min="8" max="8" width="18.1666666666667" style="4"/>
+    <col min="8" max="8" width="18.1696428571429" style="4"/>
     <col min="9" max="10" width="13" style="4"/>
-    <col min="11" max="11" width="13.1666666666667" style="4"/>
+    <col min="11" max="11" width="13.1696428571429" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="10.1666666666667" style="4"/>
-    <col min="14" max="14" width="3.66666666666667" style="4"/>
+    <col min="13" max="13" width="10.1696428571429" style="4"/>
+    <col min="14" max="14" width="3.66964285714286" style="4"/>
     <col min="15" max="15" width="5" style="4"/>
-    <col min="16" max="16" width="3.16666666666667" style="4"/>
+    <col min="16" max="16" width="3.16964285714286" style="4"/>
     <col min="17" max="18" width="9" style="4"/>
     <col min="19" max="19" width="13" style="4"/>
     <col min="20" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -15421,7 +15421,7 @@
       <c r="R25" s="11"/>
       <c r="S25" s="12"/>
     </row>
-    <row r="26" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="26" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A26" s="13" t="s">
         <v>606</v>
       </c>
@@ -15446,7 +15446,7 @@
       <c r="R26" s="9"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="27" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A27" s="13" t="s">
         <v>607</v>
       </c>
@@ -15521,7 +15521,7 @@
       <c r="R29" s="11"/>
       <c r="S29" s="12"/>
     </row>
-    <row r="30" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="30" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A30" s="13" t="s">
         <v>610</v>
       </c>
@@ -15546,7 +15546,7 @@
       <c r="R30" s="9"/>
       <c r="S30" s="19"/>
     </row>
-    <row r="31" s="45" customFormat="1" ht="12" spans="1:19">
+    <row r="31" s="45" customFormat="1" ht="15.2" spans="1:19">
       <c r="A31" s="13" t="s">
         <v>611</v>
       </c>
@@ -15971,7 +15971,7 @@
       <c r="R47" s="9"/>
       <c r="S47" s="19"/>
     </row>
-    <row r="48" s="46" customFormat="1" ht="12" spans="1:19">
+    <row r="48" s="46" customFormat="1" ht="15.2" spans="1:19">
       <c r="A48" s="13" t="s">
         <v>627</v>
       </c>
@@ -15996,7 +15996,7 @@
       <c r="R48" s="9"/>
       <c r="S48" s="19"/>
     </row>
-    <row r="49" s="46" customFormat="1" ht="12" spans="1:19">
+    <row r="49" s="46" customFormat="1" ht="15.2" spans="1:19">
       <c r="A49" s="22" t="s">
         <v>628</v>
       </c>
@@ -16509,27 +16509,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -17119,27 +17119,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -17826,27 +17826,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -18317,27 +18317,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R64"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
     <col min="3" max="3" width="24" style="35" customWidth="1"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -19711,7 +19711,7 @@
       <c r="Q57" s="11"/>
       <c r="R57" s="12"/>
     </row>
-    <row r="58" ht="24" spans="1:18">
+    <row r="58" ht="31" spans="1:18">
       <c r="A58" s="13" t="s">
         <v>680</v>
       </c>
@@ -19894,27 +19894,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -20385,27 +20385,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="定制配置（Linux未整理，勿参考）"/>
   <dimension ref="A1:R68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="28.1666666666667" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="32.6666666666667" style="2"/>
+    <col min="1" max="1" width="28.1696428571429" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="32.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -22048,27 +22048,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -23065,14 +23065,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="软件安装管理"/>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="18.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="18.3303571428571" customWidth="1"/>
     <col min="3" max="3" width="7.5" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="14.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="13.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.3303571428571" customWidth="1"/>
+    <col min="7" max="7" width="13.8303571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -23263,28 +23263,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="25.6666666666667" style="2"/>
-    <col min="3" max="3" width="61.8333333333333" style="35"/>
-    <col min="4" max="4" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="25.6696428571429" style="2"/>
+    <col min="3" max="3" width="61.8303571428571" style="35"/>
+    <col min="4" max="4" width="20.6696428571429" style="2"/>
     <col min="5" max="5" width="19" style="4"/>
     <col min="6" max="7" width="17.5" style="4"/>
-    <col min="8" max="8" width="18.1666666666667" style="4"/>
+    <col min="8" max="8" width="18.1696428571429" style="4"/>
     <col min="9" max="10" width="13" style="4"/>
-    <col min="11" max="11" width="13.1666666666667" style="4"/>
+    <col min="11" max="11" width="13.1696428571429" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="10.1666666666667" style="4"/>
-    <col min="14" max="14" width="3.66666666666667" style="4"/>
+    <col min="13" max="13" width="10.1696428571429" style="4"/>
+    <col min="14" max="14" width="3.66964285714286" style="4"/>
     <col min="15" max="15" width="5" style="4"/>
-    <col min="16" max="16" width="3.16666666666667" style="4"/>
+    <col min="16" max="16" width="3.16964285714286" style="4"/>
     <col min="17" max="18" width="9" style="4"/>
     <col min="19" max="19" width="13" style="4"/>
     <col min="20" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:19">
       <c r="A1" s="5" t="s">
         <v>318</v>
       </c>
@@ -23447,27 +23447,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -24272,27 +24272,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -25291,27 +25291,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -25974,27 +25974,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="即时通讯文件传送策略"/>
   <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="35"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="35"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -26668,7 +26668,7 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="12"/>
     </row>
-    <row r="29" ht="60" spans="1:18">
+    <row r="29" ht="76" spans="1:18">
       <c r="A29" s="22" t="s">
         <v>680</v>
       </c>
@@ -27331,27 +27331,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="35"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="35"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -28260,27 +28260,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="2"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -29303,27 +29303,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="16"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="16"/>
     <col min="4" max="4" width="19" style="4"/>
     <col min="5" max="6" width="17.5" style="4"/>
-    <col min="7" max="7" width="18.1666666666667" style="4"/>
+    <col min="7" max="7" width="18.1696428571429" style="4"/>
     <col min="8" max="9" width="13" style="4"/>
-    <col min="10" max="10" width="13.1666666666667" style="4"/>
+    <col min="10" max="10" width="13.1696428571429" style="4"/>
     <col min="11" max="11" width="5" style="4"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -29853,7 +29853,7 @@
       <c r="Q22" s="11"/>
       <c r="R22" s="12"/>
     </row>
-    <row r="23" ht="24" spans="1:18">
+    <row r="23" ht="31" spans="1:18">
       <c r="A23" s="13" t="s">
         <v>866</v>
       </c>
@@ -30215,7 +30215,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="12"/>
     </row>
-    <row r="38" ht="24" spans="1:18">
+    <row r="38" ht="31" spans="1:18">
       <c r="A38" s="22" t="s">
         <v>878</v>
       </c>
@@ -30278,26 +30278,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="16"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="16"/>
     <col min="4" max="4" width="17.5" style="4"/>
-    <col min="5" max="5" width="18.1666666666667" style="4"/>
+    <col min="5" max="5" width="18.1696428571429" style="4"/>
     <col min="6" max="7" width="13" style="4"/>
-    <col min="8" max="8" width="13.1666666666667" style="4"/>
+    <col min="8" max="8" width="13.1696428571429" style="4"/>
     <col min="9" max="9" width="5" style="4"/>
-    <col min="10" max="10" width="10.1666666666667" style="4"/>
-    <col min="11" max="11" width="3.66666666666667" style="4"/>
+    <col min="10" max="10" width="10.1696428571429" style="4"/>
+    <col min="11" max="11" width="3.66964285714286" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="3.16666666666667" style="4"/>
+    <col min="13" max="13" width="3.16964285714286" style="4"/>
     <col min="14" max="15" width="9" style="4"/>
     <col min="16" max="16" width="13" style="4"/>
     <col min="17" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -30827,7 +30827,7 @@
       <c r="O24" s="11"/>
       <c r="P24" s="12"/>
     </row>
-    <row r="25" ht="24" spans="1:16">
+    <row r="25" ht="31" spans="1:16">
       <c r="A25" s="13" t="s">
         <v>884</v>
       </c>
@@ -30873,7 +30873,7 @@
       <c r="O26" s="11"/>
       <c r="P26" s="12"/>
     </row>
-    <row r="27" ht="24" spans="1:16">
+    <row r="27" ht="31" spans="1:16">
       <c r="A27" s="13" t="s">
         <v>887</v>
       </c>
@@ -30995,26 +30995,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="16"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="16"/>
     <col min="4" max="4" width="17.5" style="4"/>
-    <col min="5" max="5" width="18.1666666666667" style="4"/>
+    <col min="5" max="5" width="18.1696428571429" style="4"/>
     <col min="6" max="7" width="13" style="4"/>
-    <col min="8" max="8" width="13.1666666666667" style="4"/>
+    <col min="8" max="8" width="13.1696428571429" style="4"/>
     <col min="9" max="9" width="5" style="4"/>
-    <col min="10" max="10" width="10.1666666666667" style="4"/>
-    <col min="11" max="11" width="3.66666666666667" style="4"/>
+    <col min="10" max="10" width="10.1696428571429" style="4"/>
+    <col min="11" max="11" width="3.66964285714286" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="3.16666666666667" style="4"/>
+    <col min="13" max="13" width="3.16964285714286" style="4"/>
     <col min="14" max="15" width="9" style="4"/>
     <col min="16" max="16" width="13" style="4"/>
     <col min="17" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -31266,26 +31266,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
     <col min="3" max="3" width="23" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.5" style="4"/>
-    <col min="5" max="5" width="18.1666666666667" style="4"/>
+    <col min="5" max="5" width="18.1696428571429" style="4"/>
     <col min="6" max="7" width="13" style="4"/>
-    <col min="8" max="8" width="13.1666666666667" style="4"/>
+    <col min="8" max="8" width="13.1696428571429" style="4"/>
     <col min="9" max="9" width="5" style="4"/>
-    <col min="10" max="10" width="10.1666666666667" style="4"/>
-    <col min="11" max="11" width="3.66666666666667" style="4"/>
+    <col min="10" max="10" width="10.1696428571429" style="4"/>
+    <col min="11" max="11" width="3.66964285714286" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="3.16666666666667" style="4"/>
+    <col min="13" max="13" width="3.16964285714286" style="4"/>
     <col min="14" max="15" width="9" style="4"/>
     <col min="16" max="16" width="13" style="4"/>
     <col min="17" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>889</v>
       </c>
@@ -31331,7 +31331,7 @@
       <c r="O2" s="11"/>
       <c r="P2" s="12"/>
     </row>
-    <row r="3" ht="24" spans="1:16">
+    <row r="3" ht="31" spans="1:16">
       <c r="A3" s="26" t="s">
         <v>891</v>
       </c>
@@ -32931,29 +32931,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="25.1666666666667" style="2"/>
-    <col min="2" max="2" width="12.6666666666667" style="2"/>
-    <col min="3" max="3" width="4.16666666666667" style="16"/>
-    <col min="4" max="4" width="27.8333333333333" style="2"/>
-    <col min="5" max="5" width="10.8333333333333" style="2"/>
-    <col min="6" max="6" width="3.66666666666667" style="4"/>
-    <col min="7" max="7" width="20.8333333333333" style="2"/>
-    <col min="8" max="8" width="10.8333333333333" style="2"/>
+    <col min="1" max="1" width="25.1696428571429" style="2"/>
+    <col min="2" max="2" width="12.6696428571429" style="2"/>
+    <col min="3" max="3" width="4.16964285714286" style="16"/>
+    <col min="4" max="4" width="27.8303571428571" style="2"/>
+    <col min="5" max="5" width="10.8303571428571" style="2"/>
+    <col min="6" max="6" width="3.66964285714286" style="4"/>
+    <col min="7" max="7" width="20.8303571428571" style="2"/>
+    <col min="8" max="8" width="10.8303571428571" style="2"/>
     <col min="9" max="9" width="4.5" style="4"/>
     <col min="10" max="10" width="22.5" style="2"/>
     <col min="11" max="11" width="8.5" style="2"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>183</v>
       </c>
@@ -32989,7 +32989,7 @@
       <c r="Q1" s="5"/>
       <c r="R1" s="5"/>
     </row>
-    <row r="2" ht="24" spans="1:18">
+    <row r="2" ht="31" spans="1:18">
       <c r="A2" s="8" t="s">
         <v>322</v>
       </c>
@@ -33577,26 +33577,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="20.6666666666667" style="3"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="20.6696428571429" style="3"/>
     <col min="4" max="4" width="17.5" style="4"/>
-    <col min="5" max="5" width="18.1666666666667" style="4"/>
+    <col min="5" max="5" width="18.1696428571429" style="4"/>
     <col min="6" max="7" width="13" style="4"/>
-    <col min="8" max="8" width="13.1666666666667" style="4"/>
+    <col min="8" max="8" width="13.1696428571429" style="4"/>
     <col min="9" max="9" width="5" style="4"/>
-    <col min="10" max="10" width="10.1666666666667" style="4"/>
-    <col min="11" max="11" width="3.66666666666667" style="4"/>
+    <col min="10" max="10" width="10.1696428571429" style="4"/>
+    <col min="11" max="11" width="3.66964285714286" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="3.16666666666667" style="4"/>
+    <col min="13" max="13" width="3.16964285714286" style="4"/>
     <col min="14" max="15" width="9" style="4"/>
     <col min="16" max="16" width="13" style="4"/>
     <col min="17" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>547</v>
       </c>
@@ -34094,29 +34094,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R110"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="17.3333333333333" style="2"/>
-    <col min="2" max="2" width="10.8333333333333" style="2"/>
-    <col min="3" max="3" width="10.3333333333333" style="16"/>
-    <col min="4" max="4" width="17.8333333333333" style="2"/>
-    <col min="5" max="5" width="10.8333333333333" style="2"/>
+    <col min="1" max="1" width="17.3303571428571" style="2"/>
+    <col min="2" max="2" width="10.8303571428571" style="2"/>
+    <col min="3" max="3" width="10.3303571428571" style="16"/>
+    <col min="4" max="4" width="17.8303571428571" style="2"/>
+    <col min="5" max="5" width="10.8303571428571" style="2"/>
     <col min="6" max="6" width="8" style="4"/>
-    <col min="7" max="7" width="16.8333333333333" style="2"/>
-    <col min="8" max="8" width="10.8333333333333" style="2"/>
+    <col min="7" max="7" width="16.8303571428571" style="2"/>
+    <col min="8" max="8" width="10.8303571428571" style="2"/>
     <col min="9" max="9" width="6.5" style="4"/>
     <col min="10" max="10" width="16" style="2"/>
-    <col min="11" max="11" width="10.8333333333333" style="2"/>
-    <col min="12" max="12" width="10.1666666666667" style="4"/>
-    <col min="13" max="13" width="3.66666666666667" style="4"/>
+    <col min="11" max="11" width="10.8303571428571" style="2"/>
+    <col min="12" max="12" width="10.1696428571429" style="4"/>
+    <col min="13" max="13" width="3.66964285714286" style="4"/>
     <col min="14" max="14" width="5" style="4"/>
-    <col min="15" max="15" width="3.16666666666667" style="4"/>
+    <col min="15" max="15" width="3.16964285714286" style="4"/>
     <col min="16" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>132</v>
       </c>
@@ -34224,7 +34224,7 @@
       <c r="Q3" s="11"/>
       <c r="R3" s="12"/>
     </row>
-    <row r="4" ht="24" spans="1:18">
+    <row r="4" ht="31" spans="1:18">
       <c r="A4" s="8" t="s">
         <v>554</v>
       </c>
@@ -35340,7 +35340,7 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="12"/>
     </row>
-    <row r="41" ht="132" spans="1:18">
+    <row r="41" ht="183" spans="1:18">
       <c r="A41" s="13" t="s">
         <v>999</v>
       </c>
@@ -36982,33 +36982,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="16.8333333333333" style="2"/>
-    <col min="2" max="2" width="10.8333333333333" style="2"/>
-    <col min="3" max="3" width="12.1666666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.8333333333333" style="2"/>
-    <col min="5" max="5" width="10.8333333333333" style="2"/>
+    <col min="1" max="1" width="16.8303571428571" style="2"/>
+    <col min="2" max="2" width="10.8303571428571" style="2"/>
+    <col min="3" max="3" width="12.1696428571429" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.8303571428571" style="2"/>
+    <col min="5" max="5" width="10.8303571428571" style="2"/>
     <col min="6" max="6" width="10.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="22.3333333333333" style="2"/>
-    <col min="8" max="8" width="10.8333333333333" style="2"/>
-    <col min="9" max="9" width="10.3333333333333" style="16"/>
-    <col min="10" max="10" width="22.3333333333333" style="2"/>
-    <col min="11" max="11" width="10.8333333333333" style="2"/>
-    <col min="12" max="12" width="10.3333333333333" style="16"/>
-    <col min="13" max="13" width="16.8333333333333" style="2"/>
-    <col min="14" max="14" width="10.8333333333333" style="2"/>
+    <col min="7" max="7" width="22.3303571428571" style="2"/>
+    <col min="8" max="8" width="10.8303571428571" style="2"/>
+    <col min="9" max="9" width="10.3303571428571" style="16"/>
+    <col min="10" max="10" width="22.3303571428571" style="2"/>
+    <col min="11" max="11" width="10.8303571428571" style="2"/>
+    <col min="12" max="12" width="10.3303571428571" style="16"/>
+    <col min="13" max="13" width="16.8303571428571" style="2"/>
+    <col min="14" max="14" width="10.8303571428571" style="2"/>
     <col min="15" max="15" width="6.5" style="4"/>
-    <col min="16" max="16" width="10.1666666666667" style="4"/>
-    <col min="17" max="17" width="3.66666666666667" style="4"/>
+    <col min="16" max="16" width="10.1696428571429" style="4"/>
+    <col min="17" max="17" width="3.66964285714286" style="4"/>
     <col min="18" max="18" width="5" style="4"/>
-    <col min="19" max="19" width="3.16666666666667" style="4"/>
+    <col min="19" max="19" width="3.16964285714286" style="4"/>
     <col min="20" max="21" width="9" style="4"/>
     <col min="22" max="22" width="13" style="4"/>
     <col min="23" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:22">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:22">
       <c r="A1" s="5" t="s">
         <v>1010</v>
       </c>
@@ -37396,7 +37396,7 @@
       <c r="U9" s="11"/>
       <c r="V9" s="12"/>
     </row>
-    <row r="10" ht="36" spans="1:22">
+    <row r="10" ht="46" spans="1:22">
       <c r="A10" s="8" t="s">
         <v>1017</v>
       </c>
@@ -37440,7 +37440,7 @@
       <c r="U10" s="11"/>
       <c r="V10" s="12"/>
     </row>
-    <row r="11" ht="36" spans="1:22">
+    <row r="11" ht="46" spans="1:22">
       <c r="A11" s="8" t="s">
         <v>560</v>
       </c>
@@ -38164,7 +38164,7 @@
       <c r="U28" s="11"/>
       <c r="V28" s="12"/>
     </row>
-    <row r="29" ht="84" spans="1:22">
+    <row r="29" ht="107" spans="1:22">
       <c r="A29" s="8" t="s">
         <v>1035</v>
       </c>
@@ -38498,7 +38498,7 @@
       <c r="U38" s="11"/>
       <c r="V38" s="12"/>
     </row>
-    <row r="39" ht="84" spans="1:22">
+    <row r="39" ht="107" spans="1:22">
       <c r="A39" s="9"/>
       <c r="B39" s="14"/>
       <c r="C39" s="11"/>
@@ -39075,7 +39075,7 @@
       <c r="U56" s="11"/>
       <c r="V56" s="12"/>
     </row>
-    <row r="57" ht="84" spans="1:22">
+    <row r="57" ht="107" spans="1:22">
       <c r="A57" s="9"/>
       <c r="B57" s="9"/>
       <c r="C57" s="11"/>
@@ -39365,7 +39365,7 @@
       <c r="U65" s="11"/>
       <c r="V65" s="12"/>
     </row>
-    <row r="66" ht="72" spans="1:22">
+    <row r="66" ht="92" spans="1:22">
       <c r="A66" s="9"/>
       <c r="B66" s="9"/>
       <c r="C66" s="11"/>
@@ -40071,7 +40071,7 @@
       <c r="U87" s="11"/>
       <c r="V87" s="12"/>
     </row>
-    <row r="88" ht="48" spans="1:22">
+    <row r="88" ht="61" spans="1:22">
       <c r="A88" s="9"/>
       <c r="B88" s="9"/>
       <c r="C88" s="11"/>
@@ -40349,7 +40349,7 @@
       <c r="U96" s="11"/>
       <c r="V96" s="12"/>
     </row>
-    <row r="97" ht="48" spans="1:22">
+    <row r="97" ht="61" spans="1:22">
       <c r="A97" s="9"/>
       <c r="B97" s="9"/>
       <c r="C97" s="11"/>
@@ -42881,27 +42881,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P58"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="7.66666666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.3333333333333" style="2"/>
-    <col min="5" max="5" width="20.1666666666667" style="2"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="7.66964285714286" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.3303571428571" style="2"/>
+    <col min="5" max="5" width="20.1696428571429" style="2"/>
     <col min="6" max="6" width="6.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="19" style="4"/>
-    <col min="8" max="8" width="13.1666666666667" style="4"/>
+    <col min="8" max="8" width="13.1696428571429" style="4"/>
     <col min="9" max="9" width="5" style="4"/>
-    <col min="10" max="10" width="10.1666666666667" style="4"/>
-    <col min="11" max="11" width="3.66666666666667" style="4"/>
+    <col min="10" max="10" width="10.1696428571429" style="4"/>
+    <col min="11" max="11" width="3.66964285714286" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="3.16666666666667" style="4"/>
+    <col min="13" max="13" width="3.16964285714286" style="4"/>
     <col min="14" max="15" width="9" style="4"/>
     <col min="16" max="16" width="13" style="4"/>
     <col min="17" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>288</v>
       </c>
@@ -44397,7 +44397,7 @@
     <tabColor rgb="FFFFFFFF"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -44408,20 +44408,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="25.1666666666667" style="2"/>
-    <col min="2" max="2" width="12.6666666666667" style="2"/>
-    <col min="3" max="3" width="61.8333333333333" style="16"/>
-    <col min="4" max="4" width="21.1666666666667" style="16"/>
-    <col min="5" max="5" width="15.8333333333333" style="16"/>
-    <col min="6" max="16" width="4.16666666666667" style="16"/>
+    <col min="1" max="1" width="25.1696428571429" style="2"/>
+    <col min="2" max="2" width="12.6696428571429" style="2"/>
+    <col min="3" max="3" width="61.8303571428571" style="16"/>
+    <col min="4" max="4" width="21.1696428571429" style="16"/>
+    <col min="5" max="5" width="15.8303571428571" style="16"/>
+    <col min="6" max="16" width="4.16964285714286" style="16"/>
     <col min="17" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>187</v>
       </c>
@@ -46021,20 +46021,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="25.1666666666667" style="2"/>
-    <col min="2" max="2" width="12.6666666666667" style="2"/>
-    <col min="3" max="3" width="61.8333333333333" style="16"/>
-    <col min="4" max="4" width="21.1666666666667" style="16"/>
-    <col min="5" max="5" width="15.8333333333333" style="16"/>
-    <col min="6" max="16" width="4.16666666666667" style="16"/>
+    <col min="1" max="1" width="25.1696428571429" style="2"/>
+    <col min="2" max="2" width="12.6696428571429" style="2"/>
+    <col min="3" max="3" width="61.8303571428571" style="16"/>
+    <col min="4" max="4" width="21.1696428571429" style="16"/>
+    <col min="5" max="5" width="15.8303571428571" style="16"/>
+    <col min="6" max="16" width="4.16964285714286" style="16"/>
     <col min="17" max="17" width="9" style="4"/>
     <col min="18" max="18" width="13" style="4"/>
     <col min="19" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:18">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:18">
       <c r="A1" s="5" t="s">
         <v>200</v>
       </c>
@@ -46308,28 +46308,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Q25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="25.1666666666667" style="2"/>
+    <col min="1" max="1" width="25.1696428571429" style="2"/>
     <col min="2" max="2" width="10" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.1666666666667" style="2"/>
+    <col min="3" max="3" width="25.1696428571429" style="2"/>
     <col min="4" max="4" width="10" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.8333333333333" style="2"/>
-    <col min="6" max="6" width="10.8333333333333" style="2"/>
-    <col min="7" max="7" width="20.8333333333333" style="2"/>
-    <col min="8" max="8" width="10.8333333333333" style="2"/>
+    <col min="5" max="5" width="27.8303571428571" style="2"/>
+    <col min="6" max="6" width="10.8303571428571" style="2"/>
+    <col min="7" max="7" width="20.8303571428571" style="2"/>
+    <col min="8" max="8" width="10.8303571428571" style="2"/>
     <col min="9" max="9" width="22.5" style="2"/>
     <col min="10" max="10" width="8.5" style="2"/>
-    <col min="11" max="11" width="10.1666666666667" style="4"/>
-    <col min="12" max="12" width="3.66666666666667" style="4"/>
+    <col min="11" max="11" width="10.1696428571429" style="4"/>
+    <col min="12" max="12" width="3.66964285714286" style="4"/>
     <col min="13" max="13" width="5" style="4"/>
-    <col min="14" max="14" width="3.16666666666667" style="4"/>
+    <col min="14" max="14" width="3.16964285714286" style="4"/>
     <col min="15" max="16" width="9" style="4"/>
     <col min="17" max="17" width="13" style="4"/>
     <col min="18" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:17">
       <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
@@ -46368,7 +46368,7 @@
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
     </row>
-    <row r="2" ht="24" spans="1:17">
+    <row r="2" ht="31" spans="1:17">
       <c r="A2" s="8" t="s">
         <v>416</v>
       </c>
@@ -46923,23 +46923,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:U12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="25.1666666666667" style="2"/>
-    <col min="2" max="2" width="12.6666666666667" style="2"/>
-    <col min="3" max="3" width="11.1666666666667" style="16" customWidth="1"/>
-    <col min="4" max="4" width="25.1666666666667" style="2"/>
-    <col min="5" max="5" width="12.6666666666667" style="2"/>
-    <col min="6" max="6" width="61.8333333333333" style="16"/>
-    <col min="7" max="7" width="21.1666666666667" style="16"/>
-    <col min="8" max="8" width="15.8333333333333" style="16"/>
-    <col min="9" max="19" width="4.16666666666667" style="16"/>
+    <col min="1" max="1" width="25.1696428571429" style="2"/>
+    <col min="2" max="2" width="12.6696428571429" style="2"/>
+    <col min="3" max="3" width="11.1696428571429" style="16" customWidth="1"/>
+    <col min="4" max="4" width="25.1696428571429" style="2"/>
+    <col min="5" max="5" width="12.6696428571429" style="2"/>
+    <col min="6" max="6" width="61.8303571428571" style="16"/>
+    <col min="7" max="7" width="21.1696428571429" style="16"/>
+    <col min="8" max="8" width="15.8303571428571" style="16"/>
+    <col min="9" max="19" width="4.16964285714286" style="16"/>
     <col min="20" max="20" width="9" style="4"/>
     <col min="21" max="21" width="13" style="4"/>
     <col min="22" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:21">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:21">
       <c r="A1" s="5" t="s">
         <v>206</v>
       </c>
@@ -47286,7 +47286,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -47297,26 +47297,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P128"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="24.3333333333333" style="2"/>
-    <col min="2" max="2" width="20.1666666666667" style="2"/>
-    <col min="3" max="3" width="87.1666666666667" style="3"/>
+    <col min="1" max="1" width="24.3303571428571" style="2"/>
+    <col min="2" max="2" width="20.1696428571429" style="2"/>
+    <col min="3" max="3" width="87.1696428571429" style="3"/>
     <col min="4" max="4" width="17.5" style="4"/>
-    <col min="5" max="5" width="18.1666666666667" style="4"/>
+    <col min="5" max="5" width="18.1696428571429" style="4"/>
     <col min="6" max="7" width="13" style="4"/>
-    <col min="8" max="8" width="13.1666666666667" style="4"/>
+    <col min="8" max="8" width="13.1696428571429" style="4"/>
     <col min="9" max="9" width="5" style="4"/>
-    <col min="10" max="10" width="10.1666666666667" style="4"/>
-    <col min="11" max="11" width="3.66666666666667" style="4"/>
+    <col min="10" max="10" width="10.1696428571429" style="4"/>
+    <col min="11" max="11" width="3.66964285714286" style="4"/>
     <col min="12" max="12" width="5" style="4"/>
-    <col min="13" max="13" width="3.16666666666667" style="4"/>
+    <col min="13" max="13" width="3.16964285714286" style="4"/>
     <col min="14" max="15" width="9" style="4"/>
     <col min="16" max="16" width="13" style="4"/>
     <col min="17" max="26" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="15.2" spans="1:16">
       <c r="A1" s="5" t="s">
         <v>437</v>
       </c>
@@ -48302,7 +48302,7 @@
       <c r="O44" s="11"/>
       <c r="P44" s="12"/>
     </row>
-    <row r="45" ht="36" spans="1:16">
+    <row r="45" ht="46" spans="1:16">
       <c r="A45" s="13" t="s">
         <v>480</v>
       </c>
@@ -48920,7 +48920,7 @@
       <c r="O72" s="11"/>
       <c r="P72" s="12"/>
     </row>
-    <row r="73" ht="36" spans="1:16">
+    <row r="73" ht="46" spans="1:16">
       <c r="A73" s="8" t="s">
         <v>504</v>
       </c>
@@ -49158,7 +49158,7 @@
       <c r="O82" s="11"/>
       <c r="P82" s="12"/>
     </row>
-    <row r="83" ht="36" spans="1:16">
+    <row r="83" ht="46" spans="1:16">
       <c r="A83" s="13" t="s">
         <v>480</v>
       </c>

--- a/Linux客户端全功能支持列表.xlsx
+++ b/Linux客户端全功能支持列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11180"/>
+    <workbookView windowWidth="28800" windowHeight="11200"/>
   </bookViews>
   <sheets>
     <sheet name="模块划分ALL" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>test8811</t>
+    <t>test881122</t>
   </si>
   <si>
     <t>基本策略</t>

--- a/Linux客户端全功能支持列表.xlsx
+++ b/Linux客户端全功能支持列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11200"/>
+    <workbookView windowWidth="28800" windowHeight="11180"/>
   </bookViews>
   <sheets>
     <sheet name="模块划分ALL" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>test881122</t>
+    <t>test88112233</t>
   </si>
   <si>
     <t>基本策略</t>
